--- a/data/trans_orig/IP07_C16_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C16_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han sufrido cyberbulling en 2023 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según si han sufrido cyberbulling en su colegio/instituto o fuera de él en 2023 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47263</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33326</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52494</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>32403</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10440</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58574</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49804</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>80434</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>68204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>88261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28620</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>51065</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4401</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6062</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21079</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18352</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22521</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>79,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19566</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16339</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>78,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>19565</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16405</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20850</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23272</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20197</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>24762</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44976</t>
+          <t>42651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,64 +2088,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,74 +2544,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>14242</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>12683</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>15084</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>13001</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15574</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>19982</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -2619,27 +2619,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2770,107 +2770,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2289</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17631</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14864</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>18924</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>76,42%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>16292</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>12872</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17743</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>69,86%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>36964</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39055</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>45844</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>83,66%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>23980</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>20371</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>26166</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>75,72%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>42517</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44499</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>66497</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69788</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -3569,107 +3569,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3145</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>752</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4014</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>46681</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>46681</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>46681</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>75183</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>75183</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>72224</t>
+          <t>75183</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3912,74 +3912,74 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>86946</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>85585</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>62411</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>60786</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>69237</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>67766</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>69586</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>80957</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>78339</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>81315</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>178</t>
@@ -3987,27 +3987,27 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>143367</t>
+          <t>156182</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>141490</t>
+          <t>154718</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>349</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>653</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4251,57 +4251,57 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>62795</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>156835</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4368,72 +4368,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>255095</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>240135</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>261993</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>172717</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>111625</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>199742</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>234539</t>
+          <t>172982</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>262989</t>
+          <t>189085</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>428671</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>340510</t>
+          <t>421382</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>459204</t>
+          <t>448408</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -4481,72 +4481,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>24872</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>91786</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4594,72 +4594,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>15630</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>13710</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4707,57 +4707,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
